--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.01448126672189</v>
+        <v>10.23985320584231</v>
       </c>
       <c r="D2" t="n">
-        <v>23.37217468235928</v>
+        <v>3.797978385883383</v>
       </c>
       <c r="E2" t="n">
-        <v>3.789774010437061</v>
+        <v>0.6158382766960218</v>
       </c>
       <c r="F2" t="n">
-        <v>7.803031378167066</v>
+        <v>1.267992598952148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.59402928759602</v>
+        <v>11.47152975923435</v>
       </c>
       <c r="D3" t="n">
-        <v>38.97823743869341</v>
+        <v>6.333963583787679</v>
       </c>
       <c r="E3" t="n">
-        <v>3.789774010437061</v>
+        <v>0.6158382766960218</v>
       </c>
       <c r="F3" t="n">
-        <v>7.803031378167066</v>
+        <v>1.267992598952148</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
